--- a/backend/data/products.xlsx
+++ b/backend/data/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tause\Downloads\belami prototype\belami-tryon\backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tause\Downloads\belami prototype\belami prototype\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27535677-4CF2-4122-AD7F-73089F32C1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26233F4-50E5-452D-A74F-F46CB4DA623E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
